--- a/tests/text archivo ej 02.xlsx
+++ b/tests/text archivo ej 02.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="145">
   <si>
     <t xml:space="preserve">IMPORTACIÓN DE TEXTURA – EJEMPLO</t>
   </si>
@@ -76,6 +76,18 @@
     <t xml:space="preserve">12.60</t>
   </si>
   <si>
+    <t xml:space="preserve">4.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.1</t>
   </si>
   <si>
@@ -91,6 +103,18 @@
     <t xml:space="preserve">12.38</t>
   </si>
   <si>
+    <t xml:space="preserve">41.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.0</t>
   </si>
   <si>
@@ -106,6 +130,18 @@
     <t xml:space="preserve">12.42</t>
   </si>
   <si>
+    <t xml:space="preserve">44.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">23.6</t>
   </si>
   <si>
@@ -121,6 +157,18 @@
     <t xml:space="preserve">12.31</t>
   </si>
   <si>
+    <t xml:space="preserve">36.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8</t>
+  </si>
+  <si>
     <t xml:space="preserve">22.4</t>
   </si>
   <si>
@@ -136,6 +184,18 @@
     <t xml:space="preserve">12.47</t>
   </si>
   <si>
+    <t xml:space="preserve">52.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.5</t>
   </si>
   <si>
@@ -151,6 +211,18 @@
     <t xml:space="preserve">12.36</t>
   </si>
   <si>
+    <t xml:space="preserve">39.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">21.0</t>
   </si>
   <si>
@@ -166,6 +238,18 @@
     <t xml:space="preserve">12.29</t>
   </si>
   <si>
+    <t xml:space="preserve">58.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">20.3</t>
   </si>
   <si>
@@ -181,6 +265,18 @@
     <t xml:space="preserve">12.44</t>
   </si>
   <si>
+    <t xml:space="preserve">46.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.8</t>
   </si>
   <si>
@@ -190,6 +286,15 @@
     <t xml:space="preserve">12.35</t>
   </si>
   <si>
+    <t xml:space="preserve">34.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9</t>
+  </si>
+  <si>
     <t xml:space="preserve">23.2</t>
   </si>
   <si>
@@ -205,6 +310,15 @@
     <t xml:space="preserve">12.39</t>
   </si>
   <si>
+    <t xml:space="preserve">48.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.5</t>
   </si>
   <si>
@@ -220,6 +334,18 @@
     <t xml:space="preserve">12.41</t>
   </si>
   <si>
+    <t xml:space="preserve">50.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">22.9</t>
   </si>
   <si>
@@ -235,6 +361,15 @@
     <t xml:space="preserve">12.33</t>
   </si>
   <si>
+    <t xml:space="preserve">37.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.5</t>
   </si>
   <si>
@@ -247,21 +382,39 @@
     <t xml:space="preserve">12.37</t>
   </si>
   <si>
+    <t xml:space="preserve">42.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.7</t>
   </si>
   <si>
     <t xml:space="preserve">25.9</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.0</t>
   </si>
   <si>
     <t xml:space="preserve">12.28</t>
   </si>
   <si>
+    <t xml:space="preserve">31.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">21.9</t>
   </si>
   <si>
@@ -277,7 +430,25 @@
     <t xml:space="preserve">12.46</t>
   </si>
   <si>
+    <t xml:space="preserve">55.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5</t>
   </si>
   <si>
     <t xml:space="preserve">26.2</t>
@@ -293,7 +464,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -325,6 +496,13 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -372,7 +550,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -391,6 +569,14 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -413,37 +599,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -516,7 +702,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -590,38 +776,38 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>208</v>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>30</v>
@@ -637,38 +823,38 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="5" t="n">
         <v>2001</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>228</v>
+      <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>29</v>
@@ -684,38 +870,38 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="5" t="n">
         <v>2002</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>253</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>230</v>
+      <c r="C5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>30</v>
@@ -731,38 +917,38 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="5" t="n">
         <v>2003</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>247</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>225</v>
+      <c r="C6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>31</v>
@@ -778,38 +964,38 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="5" t="n">
         <v>2004</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>255</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>233</v>
+      <c r="C7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>30</v>
@@ -825,38 +1011,38 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="5" t="n">
         <v>2005</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>249</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>234</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>226</v>
+      <c r="C8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>29</v>
@@ -872,38 +1058,38 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="5" t="n">
         <v>2006</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>258</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>243</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>236</v>
+      <c r="C9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>32</v>
@@ -919,38 +1105,38 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="5" t="n">
         <v>2007</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>244</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>237</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>229</v>
+      <c r="C10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>30</v>
@@ -966,38 +1152,38 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>246</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>224</v>
+      <c r="C11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>28</v>
@@ -1013,38 +1199,38 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>251</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>243</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>236</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>228</v>
+      <c r="C12" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>30</v>
@@ -1060,38 +1246,38 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>254</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>247</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>232</v>
+      <c r="C13" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>31</v>
@@ -1107,38 +1293,38 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>226</v>
+      <c r="C14" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>29</v>
@@ -1154,38 +1340,38 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>229</v>
+      <c r="C15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>30</v>
@@ -1201,38 +1387,38 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>237</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>230</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>223</v>
+      <c r="C16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>31</v>
@@ -1248,38 +1434,38 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>256</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>234</v>
+      <c r="C17" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>30</v>
@@ -1295,38 +1481,38 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>249</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>234</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>227</v>
+      <c r="C18" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="L18" s="1" t="n">
         <v>29</v>
@@ -1340,6 +1526,159 @@
       <c r="O18" s="1" t="n">
         <v>1439</v>
       </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tests/text archivo ej 02.xlsx
+++ b/tests/text archivo ej 02.xlsx
@@ -372,7 +372,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -391,6 +391,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -413,37 +417,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -638,7 +642,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>2001</v>
+        <v>1011</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
@@ -684,8 +688,8 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2002</v>
+      <c r="A5" s="5" t="n">
+        <v>1012</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
@@ -732,7 +736,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>2003</v>
+        <v>1013</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
@@ -779,7 +783,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>2004</v>
+        <v>1014</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
@@ -825,8 +829,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>2005</v>
+      <c r="A8" s="5" t="n">
+        <v>1015</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
@@ -873,7 +877,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>2006</v>
+        <v>1016</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
@@ -920,7 +924,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>2007</v>
+        <v>1017</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
@@ -966,8 +970,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>2008</v>
+      <c r="A11" s="5" t="n">
+        <v>1018</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>
@@ -1014,7 +1018,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>2009</v>
+        <v>1019</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1</v>
@@ -1061,7 +1065,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>1</v>
@@ -1107,8 +1111,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>2013</v>
+      <c r="A14" s="5" t="n">
+        <v>1021</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>1</v>
@@ -1155,7 +1159,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>2014</v>
+        <v>1022</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>1</v>
@@ -1202,7 +1206,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>2015</v>
+        <v>1023</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>1</v>
@@ -1248,8 +1252,8 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>2016</v>
+      <c r="A17" s="5" t="n">
+        <v>1024</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>1</v>
@@ -1296,7 +1300,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>2017</v>
+        <v>1025</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>1</v>

--- a/tests/text archivo ej 02.xlsx
+++ b/tests/text archivo ej 02.xlsx
@@ -103,21 +103,165 @@
     <t xml:space="preserve">24.3</t>
   </si>
   <si>
+    <t xml:space="preserve">12.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.42</t>
   </si>
   <si>
     <t xml:space="preserve">23.6</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.7</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.31</t>
   </si>
   <si>
@@ -136,154 +280,10 @@
     <t xml:space="preserve">12.47</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.6</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3</t>
   </si>
 </sst>
 </file>
@@ -372,7 +372,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -391,10 +391,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -687,9 +683,9 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
-        <v>1012</v>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>1015</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
@@ -698,16 +694,16 @@
         <v>27</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>28</v>
@@ -722,21 +718,21 @@
         <v>31</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
@@ -745,16 +741,16 @@
         <v>32</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>33</v>
@@ -769,21 +765,21 @@
         <v>36</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
@@ -792,186 +788,186 @@
         <v>37</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>30</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>1445</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
-        <v>1015</v>
+      <c r="A8" s="1" t="n">
+        <v>1018</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>249</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>234</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="L8" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>360</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>1439</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>243</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>258</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>243</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>236</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="L9" s="1" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>244</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>237</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="L10" s="1" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>60</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
-        <v>1018</v>
+      <c r="A11" s="1" t="n">
+        <v>1021</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>
@@ -980,327 +976,327 @@
         <v>55</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="L11" s="1" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>59</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>251</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>243</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>236</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>228</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>30</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>1440</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>254</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>247</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>31</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>358</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="M14" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>362</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
-        <v>1021</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>59</v>
-      </c>
       <c r="N14" s="1" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="H15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="L15" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>360</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>237</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>230</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>223</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>61</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
-        <v>1024</v>
+      <c r="A17" s="1" t="n">
+        <v>1027</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>256</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>234</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="1" t="s">
+      <c r="L17" s="1" t="n">
         <v>31</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>30</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>60</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>1440</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>1</v>
@@ -1309,40 +1305,40 @@
         <v>85</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="J18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="L18" s="1" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>1439</v>
+        <v>1445</v>
       </c>
     </row>
   </sheetData>

--- a/tests/text archivo ej 02.xlsx
+++ b/tests/text archivo ej 02.xlsx
@@ -293,7 +293,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -325,6 +325,13 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -372,7 +379,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -391,6 +398,14 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -413,37 +428,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -516,7 +531,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -629,11 +644,11 @@
       <c r="M3" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>1440</v>
+      <c r="N3" s="5" t="n">
+        <v>21600</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>86400</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -676,11 +691,11 @@
       <c r="M4" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="N4" s="1" t="n">
-        <v>362</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>1443</v>
+      <c r="N4" s="5" t="n">
+        <v>21720</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>86580</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -723,11 +738,11 @@
       <c r="M5" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N5" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>1439</v>
+      <c r="N5" s="5" t="n">
+        <v>21600</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>86340</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -770,11 +785,11 @@
       <c r="M6" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="N6" s="1" t="n">
-        <v>363</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>1441</v>
+      <c r="N6" s="5" t="n">
+        <v>21780</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>86460</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -817,11 +832,11 @@
       <c r="M7" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N7" s="1" t="n">
-        <v>358</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>1437</v>
+      <c r="N7" s="5" t="n">
+        <v>21480</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>86220</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -864,11 +879,11 @@
       <c r="M8" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="N8" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>1444</v>
+      <c r="N8" s="5" t="n">
+        <v>21600</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>86640</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -911,11 +926,11 @@
       <c r="M9" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="N9" s="1" t="n">
-        <v>359</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>1440</v>
+      <c r="N9" s="5" t="n">
+        <v>21540</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>86400</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -958,11 +973,11 @@
       <c r="M10" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N10" s="1" t="n">
-        <v>362</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>1438</v>
+      <c r="N10" s="5" t="n">
+        <v>21720</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>86280</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1005,11 +1020,11 @@
       <c r="M11" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="N11" s="1" t="n">
-        <v>361</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>1443</v>
+      <c r="N11" s="5" t="n">
+        <v>21660</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>86580</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1052,11 +1067,11 @@
       <c r="M12" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N12" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>1442</v>
+      <c r="N12" s="5" t="n">
+        <v>21600</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>86520</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1099,11 +1114,11 @@
       <c r="M13" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>358</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>1441</v>
+      <c r="N13" s="5" t="n">
+        <v>21480</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>86460</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1146,11 +1161,11 @@
       <c r="M14" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N14" s="1" t="n">
-        <v>359</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>1440</v>
+      <c r="N14" s="5" t="n">
+        <v>21540</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>86400</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1193,11 +1208,11 @@
       <c r="M15" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="N15" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>1439</v>
+      <c r="N15" s="5" t="n">
+        <v>21600</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>86340</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1240,11 +1255,11 @@
       <c r="M16" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="N16" s="1" t="n">
-        <v>359</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>1438</v>
+      <c r="N16" s="5" t="n">
+        <v>21540</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>86280</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1287,11 +1302,11 @@
       <c r="M17" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="N17" s="1" t="n">
-        <v>361</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>1442</v>
+      <c r="N17" s="5" t="n">
+        <v>21660</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>86520</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1334,12 +1349,114 @@
       <c r="M18" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="N18" s="1" t="n">
-        <v>357</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>1445</v>
-      </c>
+      <c r="N18" s="5" t="n">
+        <v>21420</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>86700</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tests/text archivo ej 02.xlsx
+++ b/tests/text archivo ej 02.xlsx
@@ -400,11 +400,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -428,37 +428,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
